--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
@@ -14816,125 +14816,125 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>T33</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>障がい計画　成果目標とサービス見込量の算定</t>
+          <t>否定試験（点検スクリプトが誤りを捕まえるかの試験）</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
+          <t>点検が通っていることと、点検が働いていることは別である。わざと誤った値を入れて、点検が止まるかを確かめる。外部条件に依存しない</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>障がい計画 素案 第2版</t>
+          <t>check_ono_hitei.py（否定試験13件）</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>障がい 6-3／障がい 6-4</t>
+          <t>11-1／11-4</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>10月16日（金）</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月15日（木）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>T33</t>
+          <t>T34</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>否定試験（点検スクリプトが誤りを捕まえるかの試験）</t>
+          <t>色覚への配慮の点検（図の色と凡例）</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>点検が通っていることと、点検が働いていることは別である。わざと誤った値を入れて、点検が止まるかを確かめる。外部条件に依存しない</t>
+          <t>図はすべて当方が ono_figs で作っており、手元で確かめられる。色だけで区別させていないか、印刷の白黒で読めるかを点検する</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>11_品質管理／否定試験の記録</t>
+          <t>check_ono_shikikaku.py（配色の点検）</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>11-1／11-4</t>
+          <t>11-3</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月15日（木）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>T34</t>
+          <t>T32</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>色覚への配慮の点検（図の色と凡例）</t>
+          <t>障がい計画　成果目標とサービス見込量の算定</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>図はすべて当方が ono_figs で作っており、手元で確かめられる。色だけで区別させていないか、印刷の白黒で読めるかを点検する</t>
+          <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>11_品質管理／図の色の点検</t>
+          <t>障がい計画 素案 第2版</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>障がい 6-3／障がい 6-4</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>10月19日（月）</t>
+          <t>10月16日（金）</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -15018,7 +15018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15134,16 +15134,16 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>T33</t>
+          <t>T35</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>否定試験（点検スクリプトが誤りを捕まえるかの試験）</t>
+          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
@@ -15152,108 +15152,42 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>11-1／11-4</t>
+          <t>11-4</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>10月19日（月）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>── 10月19日（月） 計</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>T34</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>色覚への配慮の点検（図の色と凡例）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>11-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>T35</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>11-4</t>
-        </is>
-      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>残2.0h</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>── 10月19日（月） 計</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>残7.0h</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>※ 10月16日（金）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
@@ -5708,12 +5708,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="I9" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>73.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>-13.3</v>
+        <v>-12.4</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>3</v>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
+          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -5795,9 +5795,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="I10" s="13" t="n">
@@ -5810,7 +5810,7 @@
         <v>-12.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
+          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
         </is>
       </c>
     </row>
@@ -5831,17 +5831,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5851,39 +5851,39 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I11" s="13" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>82.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>-12.4</v>
+        <v>-6.4</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="15" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
+          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H12" s="16" t="inlineStr">
@@ -5932,13 +5932,13 @@
         <v>30</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
@@ -5959,17 +5959,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5984,25 +5984,25 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I13" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>35.5</v>
+        <v>100</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M13" s="17" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6066,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="17" t="inlineStr">
         <is>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -6279,17 +6279,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -6363,24 +6363,24 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I19" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K19" s="13" t="n">
         <v>0</v>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
         </is>
       </c>
     </row>
@@ -6471,17 +6471,17 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -6491,30 +6491,30 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" s="17" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6727,17 +6727,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -6811,24 +6811,24 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I26" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="13" t="n">
         <v>0</v>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -6924,12 +6924,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -6983,32 +6983,32 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -7052,27 +7052,27 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -7111,17 +7111,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
@@ -7175,50 +7175,50 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7244,27 +7244,27 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
@@ -7303,44 +7303,44 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I34" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K34" s="13" t="n">
         <v>0</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -7372,17 +7372,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
@@ -7431,17 +7431,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -7451,24 +7451,24 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36" s="13" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7495,44 +7495,44 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I37" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K37" s="13" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
         </is>
       </c>
     </row>
@@ -7559,50 +7559,50 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" s="17" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
+          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>障がい計画　予定進捗率 57.3％　対　実績進捗率 57.4％　乖離 +0.2ポイント　／　おおむね予定どおり 28件／前倒し 11件／期限超過（1か月） 5件／遅れ 4件／期限超過（2か月） 1件</t>
+          <t>障がい計画　予定進捗率 57.3％　対　実績進捗率 57.8％　乖離 +0.5ポイント　／　おおむね予定どおり 29件／前倒し 11件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14906,45 +14906,45 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>T36</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>障がい計画　成果目標とサービス見込量の算定</t>
+          <t>前回計画から手帳所持者数の推移を取り出し、素案と図に反映</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
+          <t>前回計画（令和6年3月）が令和元年〜令和5年の5か年を図に載せている。手元の原本から取り出せるため、町の回答を待たずに進む。内訳の和が前回計画の「計」と一致することを自己点検で確かめる</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>障がい計画 素案 第2版</t>
+          <t>障がい計画 素案 第1部第2章2／図 f61_techo</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>障がい 6-3／障がい 6-4</t>
+          <t>障がい 5-2</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>10月16日（金）</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月15日（木）</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>素案 第1版ができたため、高齢者と同じ点検に載せられる。体裁37件・紙面18件の対象に加え済みで、残るのは図の追加</t>
+          <t>素案 第1版ができたため、高齢者と同じ点検に載せられる。体裁37件・紙面18件の対象に加え、図を1点置いた（T36）。サービス実績の図は、実績を受領してから作る</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -14979,29 +14979,74 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画　成果目標とサービス見込量の算定</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画 素案 第2版</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>障がい 6-3／障がい 6-4</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>10月16日（金）</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>※ 合計 98.0時間（1日 8.0時間として約12.2日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>※ 合計 100.5時間（1日 8.0時間として約12.6日）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>※ 「なぜ今できるか」に町の回答待ちが混ざっている項目があると、ブックの生成が止まります。</t>
         </is>
@@ -15018,7 +15063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15123,71 +15168,15 @@
       </c>
       <c r="G3" s="20" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>T35</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>11-4</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>── 10月19日（月） 計</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>残2.0h</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>※ 10月16日（金）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
@@ -5708,17 +5708,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -5731,9 +5731,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="I9" s="13" t="n">
@@ -5746,7 +5746,7 @@
         <v>-12.4</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
+          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
         </is>
       </c>
     </row>
@@ -5767,17 +5767,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -5787,39 +5787,39 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I10" s="13" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>82.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>-12.4</v>
+        <v>-6.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
+          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
         </is>
       </c>
     </row>
@@ -5831,32 +5831,32 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H11" s="16" t="inlineStr">
@@ -5868,13 +5868,13 @@
         <v>30</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
@@ -5895,17 +5895,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5920,25 +5920,25 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I12" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>35.5</v>
+        <v>100</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5959,17 +5959,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13" s="17" t="inlineStr">
         <is>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -6215,17 +6215,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -6279,17 +6279,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -6299,24 +6299,24 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I18" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="13" t="n">
         <v>0</v>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -6348,12 +6348,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
         </is>
       </c>
     </row>
@@ -6407,17 +6407,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6427,30 +6427,30 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" s="17" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
@@ -6727,17 +6727,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6747,24 +6747,24 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I25" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25" s="13" t="n">
         <v>0</v>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
@@ -6791,32 +6791,32 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6919,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -6988,27 +6988,27 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -7047,17 +7047,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
@@ -7111,50 +7111,50 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I31" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" s="17" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7180,27 +7180,27 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
@@ -7239,44 +7239,44 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I33" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K33" s="13" t="n">
         <v>0</v>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -7308,17 +7308,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
@@ -7367,17 +7367,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -7387,24 +7387,24 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35" s="13" t="n">
         <v>0</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7431,44 +7431,44 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I36" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K36" s="13" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
         </is>
       </c>
     </row>
@@ -7495,50 +7495,50 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M37" s="17" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
+          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>73.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>3</v>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
+          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>障がい計画　予定進捗率 57.3％　対　実績進捗率 57.8％　乖離 +0.5ポイント　／　おおむね予定どおり 29件／前倒し 11件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
+          <t>障がい計画　予定進捗率 57.3％　対　実績進捗率 58.2％　乖離 +0.9ポイント　／　おおむね予定どおり 30件／前倒し 11件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14906,30 +14906,30 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>T36</t>
+          <t>T37</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>前回計画から手帳所持者数の推移を取り出し、素案と図に反映</t>
+          <t>前回計画から第6期の実績・第7期の見込量を読み取り、素案に反映</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>前回計画（令和6年3月）が令和元年〜令和5年の5か年を図に載せている。手元の原本から取り出せるため、町の回答を待たずに進む。内訳の和が前回計画の「計」と一致することを自己点検で確かめる</t>
+          <t>前回計画（128頁）は手元にあり、サービスごとの見込量と実績を載せている。町にお尋ねするまでもない。書き写さず、原本のPDFを毎回読む形にすれば、原本から離れない</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>障がい計画 素案 第1部第2章2／図 f61_techo</t>
+          <t>ono_shogai_zenkai.py（44サービス）／素案 第1部第3章2</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>障がい 5-2</t>
+          <t>障がい 5-1／障がい 6-4</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -14951,30 +14951,30 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>T35</t>
+          <t>T36</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
+          <t>前回計画から手帳所持者数の推移を取り出し、素案と図に反映</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>素案 第1版ができたため、高齢者と同じ点検に載せられる。体裁37件・紙面18件の対象に加え、図を1点置いた（T36）。サービス実績の図は、実績を受領してから作る</t>
+          <t>前回計画（令和6年3月）が令和元年〜令和5年の5か年を図に載せている。手元の原本から取り出せるため、町の回答を待たずに進む。内訳の和が前回計画の「計」と一致することを自己点検で確かめる</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>11_品質管理／点検の対象の拡大</t>
+          <t>障がい計画 素案 第1部第2章2／図 f61_techo</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>障がい 5-2</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -14996,57 +14996,102 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>素案 第1版ができたため、高齢者と同じ点検に載せられる。体裁37件・紙面18件の対象に加え、図を1点置いた（T36）。サービス実績の図は、実績を受領してから作る</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>11_品質管理／点検の対象の拡大</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>11-4</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>T32</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>障がい計画　成果目標とサービス見込量の算定</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D38" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>障がい計画 素案 第2版</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>障がい 6-3／障がい 6-4</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>10月16日（金）</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>※ 合計 100.5時間（1日 8.0時間として約12.6日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>※ 合計 104.5時間（1日 8.0時間として約13.1日）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>※ 「なぜ今できるか」に町の回答待ちが混ざっている項目があると、ブックの生成が止まります。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261015.xlsx
@@ -5767,32 +5767,32 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H10" s="16" t="inlineStr">
@@ -5804,13 +5804,13 @@
         <v>30</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10" s="17" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
@@ -5831,17 +5831,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5856,25 +5856,25 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I11" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>35.5</v>
+        <v>100</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5895,17 +5895,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -5959,17 +5959,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -6215,17 +6215,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6235,24 +6235,24 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I17" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K17" s="13" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
         </is>
       </c>
     </row>
@@ -6343,17 +6343,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -6363,30 +6363,30 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M19" s="17" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6599,17 +6599,17 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6683,24 +6683,24 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I24" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="13" t="n">
         <v>0</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
@@ -6727,32 +6727,32 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -6924,27 +6924,27 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -6983,17 +6983,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
@@ -7047,50 +7047,50 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7116,27 +7116,27 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
@@ -7175,44 +7175,44 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="13" t="n">
         <v>0</v>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -7244,17 +7244,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
@@ -7303,17 +7303,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -7323,24 +7323,24 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34" s="13" t="n">
         <v>0</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7367,44 +7367,44 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I35" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="13" t="n">
         <v>0</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
         </is>
       </c>
     </row>
@@ -7431,50 +7431,50 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36" s="17" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
+          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="I37" s="13" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>73.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>3</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
+          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -7559,17 +7559,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>2-15</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>介護保険の利用の有無による問31の再集計</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -7587,19 +7587,19 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>82.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>3</v>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
+          <t>個票（1件ごとの回答データ）。集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
@@ -7623,47 +7623,47 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I39" s="13" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>46.7</v>
+        <v>36.4</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>3</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>個票（1件ごとの回答データ）。集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
+          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
         </is>
       </c>
     </row>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H40" s="16" t="inlineStr">
@@ -7721,16 +7721,16 @@
         </is>
       </c>
       <c r="I40" s="13" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>28.9</v>
+        <v>69.7</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>11.1</v>
+        <v>20.3</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" s="18" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
@@ -7751,17 +7751,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7785,13 +7785,13 @@
         </is>
       </c>
       <c r="I41" s="13" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>69.7</v>
+        <v>48.9</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>3</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>レビュー所見の反映（重大5件）。うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
@@ -7815,17 +7815,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H42" s="16" t="inlineStr">
@@ -7849,16 +7849,16 @@
         </is>
       </c>
       <c r="I42" s="13" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>48.9</v>
+        <v>15.4</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>21.1</v>
+        <v>24.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>レビュー所見の反映（重大5件）。うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>レビュー所見の反映（重大5件）、ヒアリング記録の完成</t>
         </is>
       </c>
     </row>
@@ -7879,17 +7879,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H43" s="16" t="inlineStr">
@@ -7913,13 +7913,13 @@
         </is>
       </c>
       <c r="I43" s="13" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>15.4</v>
+        <v>28.9</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>4</v>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>レビュー所見の反映（重大5件）、ヒアリング記録の完成</t>
+          <t>A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>障がい計画　予定進捗率 57.3％　対　実績進捗率 58.2％　乖離 +0.9ポイント　／　おおむね予定どおり 30件／前倒し 11件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
+          <t>障がい計画　予定進捗率 57.3％　対　実績進捗率 59.0％　乖離 +1.8ポイント　／　おおむね予定どおり 30件／前倒し 11件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14906,30 +14906,30 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>T37</t>
+          <t>T40</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>前回計画から第6期の実績・第7期の見込量を読み取り、素案に反映</t>
+          <t>地域生活支援事業の実績が0であることの洗い出し</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>前回計画（128頁）は手元にあり、サービスごとの見込量と実績を載せている。町にお尋ねするまでもない。書き写さず、原本のPDFを毎回読む形にすれば、原本から離れない</t>
+          <t>前回計画の第3部第8章に11事業が載っている。読めば、どの事業が0のままなのかがすぐ分かる。町の回答を待たない</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>ono_shogai_zenkai.py（44サービス）／素案 第1部第3章2</t>
+          <t>素案 第3部第2章2-2</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>障がい 5-1／障がい 6-4</t>
+          <t>障がい 6-4</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -14951,30 +14951,30 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>T36</t>
+          <t>T39</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>前回計画から手帳所持者数の推移を取り出し、素案と図に反映</t>
+          <t>前回計画の成果目標の検証（成り立たない目標の洗い出し）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>前回計画（令和6年3月）が令和元年〜令和5年の5か年を図に載せている。手元の原本から取り出せるため、町の回答を待たずに進む。内訳の和が前回計画の「計」と一致することを自己点検で確かめる</t>
+          <t>前回計画は手元にあり、目標値と基準人数が同じ頁に載っている。割り算をするだけで成り立つかどうかが分かる。町の回答を待たない</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>障がい計画 素案 第1部第2章2／図 f61_techo</t>
+          <t>素案 第3部第1章1-1</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>障がい 5-2</t>
+          <t>障がい 6-3</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -14996,30 +14996,30 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>T35</t>
+          <t>T38</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
+          <t>障がい計画　見込量の置き方を「人数×1人あたり日数」に具体化</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>素案 第1版ができたため、高齢者と同じ点検に載せられる。体裁37件・紙面18件の対象に加え、図を1点置いた（T36）。サービス実績の図は、実績を受領してから作る</t>
+          <t>T37で読み取った第6期の実績から、1人あたり日数が算出できる。量が見込みを下回った原因が人数ではなく日数にあることが分かるため、置き方をここで決められる。値そのものは実績の受領を待つ</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>11_品質管理／点検の対象の拡大</t>
+          <t>素案 第3部第2章2-1／図 f62_shogai_nissu</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>障がい 6-4</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -15041,57 +15041,192 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>前回計画から第6期の実績・第7期の見込量を読み取り、素案に反映</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>前回計画（128頁）は手元にあり、サービスごとの見込量と実績を載せている。町にお尋ねするまでもない。書き写さず、原本のPDFを毎回読む形にすれば、原本から離れない</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>ono_shogai_zenkai.py（44サービス）／素案 第1部第3章2</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>障がい 5-1／障がい 6-4</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>前回計画から手帳所持者数の推移を取り出し、素案と図に反映</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>前回計画（令和6年3月）が令和元年〜令和5年の5か年を図に載せている。手元の原本から取り出せるため、町の回答を待たずに進む。内訳の和が前回計画の「計」と一致することを自己点検で確かめる</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画 素案 第1部第2章2／図 f61_techo</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>障がい 5-2</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画　素案の体裁・紙面の点検を高齢者と同じ水準にする</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>素案 第1版ができたため、高齢者と同じ点検に載せられる。体裁37件・紙面18件の対象に加え、図を1点置いた（T36）。サービス実績の図は、実績を受領してから作る</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>11_品質管理／点検の対象の拡大</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>11-4</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>10月15日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>T32</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>障がい計画　成果目標とサービス見込量の算定</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D41" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>障がい計画 素案 第2版</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>障がい 6-3／障がい 6-4</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>10月16日（金）</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>※ 合計 104.5時間（1日 8.0時間として約13.1日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>※ 合計 110.5時間（1日 8.0時間として約13.8日）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>※ 「なぜ今できるか」に町の回答待ちが混ざっている項目があると、ブックの生成が止まります。</t>
         </is>
